--- a/case_studies/base_case_50_5_dd/2030/technologies.xlsx
+++ b/case_studies/base_case_50_5_dd/2030/technologies.xlsx
@@ -691,10 +691,10 @@
         <v>0</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>53.53</v>
+        <v>54.48</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>150.56</v>
+        <v>153.14</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0</v>
@@ -712,16 +712,16 @@
         <v>0</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>135.49</v>
+        <v>137.9</v>
       </c>
       <c r="Q2" s="3" t="n">
         <v>184.21</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>36.8</v>
+        <v>37.46</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>22.37</v>
+        <v>21.27</v>
       </c>
       <c r="T2" s="3" t="n">
         <v>159.94</v>
@@ -730,10 +730,10 @@
         <v>0</v>
       </c>
       <c r="V2" s="3" t="n">
-        <v>49.16</v>
+        <v>46.73</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>23.43</v>
+        <v>24.75</v>
       </c>
       <c r="X2" s="3" t="n">
         <v>0</v>
@@ -1064,7 +1064,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0</v>
+        <v>62.79</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
@@ -1073,19 +1073,19 @@
         <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>55.06</v>
+        <v>67.88</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>141.59</v>
+        <v>117.49</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
+        <v>42.99</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>0</v>
@@ -1100,16 +1100,16 @@
         <v>0</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>139.37</v>
+        <v>121.74</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>139.37</v>
+        <v>135.21</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>37.86</v>
+        <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0</v>
+        <v>9.16</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>95.54000000000001</v>
@@ -1121,7 +1121,7 @@
         <v>0</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>37.86</v>
+        <v>0</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>0</v>
@@ -1130,7 +1130,7 @@
         <v>0</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0</v>
+        <v>59.12</v>
       </c>
       <c r="AA6" s="3" t="n">
         <v>0</v>
@@ -1203,10 +1203,10 @@
         <v>0</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>18.48</v>
+        <v>19.77</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>15.14</v>
+        <v>15.76</v>
       </c>
       <c r="T7" s="5" t="n">
         <v>48.52</v>
@@ -1215,10 +1215,10 @@
         <v>0</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>0.36</v>
+        <v>1.14</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>18.38</v>
+        <v>19.46</v>
       </c>
       <c r="X7" s="5" t="n">
         <v>0</v>
@@ -1273,10 +1273,10 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>160.06</v>
+        <v>166.47</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
@@ -1285,25 +1285,25 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>386.97</v>
+        <v>653.27</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>386.97</v>
+        <v>653.27</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>165.54</v>
+        <v>171.53</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>219.98</v>
+        <v>208.42</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>44.97</v>
+        <v>46.59</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>36.8</v>
+        <v>25.1</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>110.4</v>
@@ -1312,10 +1312,10 @@
         <v>0</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>44.67</v>
+        <v>46.59</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>0</v>

--- a/case_studies/base_case_50_5_dd/2030/technologies.xlsx
+++ b/case_studies/base_case_50_5_dd/2030/technologies.xlsx
@@ -994,7 +994,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>745.4</v>
+        <v>643.22</v>
       </c>
       <c r="N5" s="5" t="n">
         <v>745.4</v>
@@ -1079,10 +1079,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>67.88</v>
+        <v>69.53</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>117.49</v>
+        <v>118.43</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>42.99</v>
@@ -1091,7 +1091,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>565.33</v>
+        <v>396.62</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>565.33</v>
@@ -1100,16 +1100,16 @@
         <v>0</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>121.74</v>
+        <v>126.14</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>135.21</v>
+        <v>139.37</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>9.16</v>
+        <v>9</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>95.54000000000001</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>48.52</v>
+        <v>28.97</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>59.3</v>
@@ -1203,10 +1203,10 @@
         <v>0</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>19.77</v>
+        <v>19.92</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>15.76</v>
+        <v>15.88</v>
       </c>
       <c r="T7" s="5" t="n">
         <v>48.52</v>
@@ -1218,7 +1218,7 @@
         <v>1.14</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>19.46</v>
+        <v>19.61</v>
       </c>
       <c r="X7" s="5" t="n">
         <v>0</v>
@@ -1285,7 +1285,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>653.27</v>
+        <v>400.96</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>653.27</v>

--- a/case_studies/base_case_50_5_dd/2030/technologies.xlsx
+++ b/case_studies/base_case_50_5_dd/2030/technologies.xlsx
@@ -691,10 +691,10 @@
         <v>0</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>54.48</v>
+        <v>51.54</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>153.14</v>
+        <v>140.61</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0</v>
@@ -712,13 +712,13 @@
         <v>0</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>137.9</v>
+        <v>130.46</v>
       </c>
       <c r="Q2" s="3" t="n">
         <v>184.21</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>37.46</v>
+        <v>35.44</v>
       </c>
       <c r="S2" s="3" t="n">
         <v>21.27</v>
@@ -730,10 +730,10 @@
         <v>0</v>
       </c>
       <c r="V2" s="3" t="n">
-        <v>46.73</v>
+        <v>69.83</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>24.75</v>
+        <v>16.44</v>
       </c>
       <c r="X2" s="3" t="n">
         <v>0</v>
@@ -994,7 +994,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>643.22</v>
+        <v>745.4</v>
       </c>
       <c r="N5" s="5" t="n">
         <v>745.4</v>
@@ -1079,10 +1079,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>69.53</v>
+        <v>67.83</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>118.43</v>
+        <v>117.43</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>42.99</v>
@@ -1091,7 +1091,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>396.62</v>
+        <v>565.33</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>565.33</v>
@@ -1100,16 +1100,16 @@
         <v>0</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>126.14</v>
+        <v>121.61</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>139.37</v>
+        <v>135.45</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>9</v>
+        <v>9.42</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>95.54000000000001</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>28.97</v>
+        <v>48.52</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>59.3</v>
@@ -1203,10 +1203,10 @@
         <v>0</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>19.92</v>
+        <v>19.87</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>15.88</v>
+        <v>15.58</v>
       </c>
       <c r="T7" s="5" t="n">
         <v>48.52</v>
@@ -1215,10 +1215,10 @@
         <v>0</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>1.14</v>
+        <v>1.73</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>19.61</v>
+        <v>19.4</v>
       </c>
       <c r="X7" s="5" t="n">
         <v>0</v>
@@ -1285,7 +1285,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>400.96</v>
+        <v>653.27</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>653.27</v>

--- a/case_studies/base_case_50_5_dd/2030/technologies.xlsx
+++ b/case_studies/base_case_50_5_dd/2030/technologies.xlsx
@@ -1067,7 +1067,7 @@
         <v>62.79</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
@@ -1261,10 +1261,10 @@
         <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>

--- a/case_studies/base_case_50_5_dd/2030/technologies.xlsx
+++ b/case_studies/base_case_50_5_dd/2030/technologies.xlsx
@@ -1067,10 +1067,10 @@
         <v>62.79</v>
       </c>
       <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>11.11</v>
@@ -1261,10 +1261,10 @@
         <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -1285,7 +1285,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>653.27</v>
+        <v>400.96</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>653.27</v>
